--- a/data/raw/inventory/Week 35/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -547,10 +547,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>60</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -671,10 +671,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
         <v>12</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
         <v>39</v>
@@ -5123,7 +5123,7 @@
         <v>22</v>
       </c>
       <c r="F76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
         <v>23</v>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F80" t="n">
         <v>63</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>4</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F88" t="n">
         <v>10</v>
@@ -5879,10 +5879,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -6859,7 +6859,7 @@
         <v>51</v>
       </c>
       <c r="F104" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
         <v>51</v>
@@ -7045,7 +7045,7 @@
         <v>24</v>
       </c>
       <c r="F107" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K107" t="n">
         <v>24</v>
@@ -7293,7 +7293,7 @@
         <v>28</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
         <v>28</v>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F113" t="n">
         <v>11</v>
@@ -7429,10 +7429,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>5</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
         <v>6</v>
@@ -8533,7 +8533,7 @@
         <v>63</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K131" t="n">
         <v>63</v>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F156" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -10098,7 +10098,7 @@
         <v>3</v>
       </c>
       <c r="K156" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -10393,7 +10393,7 @@
         <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G161" t="n">
         <v>6</v>
@@ -10405,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K161" t="n">
         <v>43</v>
@@ -10455,7 +10455,7 @@
         <v>19</v>
       </c>
       <c r="F162" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G162" t="n">
         <v>12</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
         <v>19</v>
@@ -11633,7 +11633,7 @@
         <v>165</v>
       </c>
       <c r="F181" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
         <v>24</v>
       </c>
       <c r="J181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K181" t="n">
         <v>165</v>

--- a/data/raw/inventory/Week 35/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
         <v>27</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>11</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F34" t="n">
         <v>33</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F36" t="n">
         <v>39</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>97</v>
       </c>
       <c r="F49" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
         <v>97</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" t="n">
         <v>13</v>
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         <v>29</v>
       </c>
       <c r="F71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
         <v>20</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>29</v>
@@ -5619,7 +5619,7 @@
         <v>153</v>
       </c>
       <c r="F84" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>154</v>
@@ -6797,7 +6797,7 @@
         <v>49</v>
       </c>
       <c r="F103" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" t="n">
         <v>49</v>
@@ -6859,7 +6859,7 @@
         <v>51</v>
       </c>
       <c r="F104" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K104" t="n">
         <v>51</v>
@@ -7293,7 +7293,7 @@
         <v>28</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
         <v>28</v>
@@ -8347,7 +8347,7 @@
         <v>12</v>
       </c>
       <c r="F128" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
         <v>12</v>
